--- a/dev/CodeSystem-PSOC.xlsx
+++ b/dev/CodeSystem-PSOC.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T03:12:48+00:00</t>
+    <t>2026-03-18T09:54:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSOC.xlsx
+++ b/dev/CodeSystem-PSOC.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T09:54:13+00:00</t>
+    <t>2026-03-23T13:24:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSOC.xlsx
+++ b/dev/CodeSystem-PSOC.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:24:52+00:00</t>
+    <t>2026-03-25T02:48:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSOC.xlsx
+++ b/dev/CodeSystem-PSOC.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T02:48:03+00:00</t>
+    <t>2026-03-25T03:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSOC.xlsx
+++ b/dev/CodeSystem-PSOC.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:05:28+00:00</t>
+    <t>2026-03-25T03:10:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSOC.xlsx
+++ b/dev/CodeSystem-PSOC.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:10:05+00:00</t>
+    <t>2026-03-25T03:15:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSOC.xlsx
+++ b/dev/CodeSystem-PSOC.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:15:34+00:00</t>
+    <t>2026-03-25T03:26:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSOC.xlsx
+++ b/dev/CodeSystem-PSOC.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:26:10+00:00</t>
+    <t>2026-03-25T03:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSOC.xlsx
+++ b/dev/CodeSystem-PSOC.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:31:02+00:00</t>
+    <t>2026-03-25T03:34:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSOC.xlsx
+++ b/dev/CodeSystem-PSOC.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:34:45+00:00</t>
+    <t>2026-03-25T03:48:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSOC.xlsx
+++ b/dev/CodeSystem-PSOC.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:48:45+00:00</t>
+    <t>2026-03-25T03:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSOC.xlsx
+++ b/dev/CodeSystem-PSOC.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:54:03+00:00</t>
+    <t>2026-04-01T03:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSOC.xlsx
+++ b/dev/CodeSystem-PSOC.xlsx
@@ -7,12 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
+    <sheet name="Concepts" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
   <si>
     <t>Property</t>
   </si>
@@ -23,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://doh.gov.ph/fhir/ph-core/CodeSystem/PSOC</t>
+    <t>https://psa.gov.ph/classification/psoc/unit</t>
   </si>
   <si>
     <t>Version</t>
@@ -59,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:21:07+00:00</t>
+    <t>2026-04-01T03:34:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -77,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Philippines</t>
+    <t>Philippines (the)</t>
   </si>
   <si>
     <t>Description</t>
@@ -110,13 +111,64 @@
     <t>Content</t>
   </si>
   <si>
-    <t>not-present</t>
+    <t>example</t>
   </si>
   <si>
     <t>Supplements</t>
   </si>
   <si>
     <t>Count</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>111102</t>
+  </si>
+  <si>
+    <t>Hospital Administrator</t>
+  </si>
+  <si>
+    <t>Manages hospital operations</t>
+  </si>
+  <si>
+    <t>111103</t>
+  </si>
+  <si>
+    <t>Medical Department Head</t>
+  </si>
+  <si>
+    <t>Head of a medical department</t>
+  </si>
+  <si>
+    <t>121101</t>
+  </si>
+  <si>
+    <t>General Manager</t>
+  </si>
+  <si>
+    <t>Manages overall operations of an organization</t>
+  </si>
+  <si>
+    <t>211101</t>
+  </si>
+  <si>
+    <t>Medical Doctor</t>
+  </si>
+  <si>
+    <t>Licensed physician practicing medicine</t>
   </si>
 </sst>
 </file>
@@ -420,4 +472,84 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>35</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/dev/CodeSystem-PSOC.xlsx
+++ b/dev/CodeSystem-PSOC.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:34:09+00:00</t>
+    <t>2026-04-01T03:44:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSOC.xlsx
+++ b/dev/CodeSystem-PSOC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:44:59+00:00</t>
+    <t>2026-04-06T07:53:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSOC.xlsx
+++ b/dev/CodeSystem-PSOC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-06T07:53:57+00:00</t>
+    <t>2026-04-08T04:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSOC.xlsx
+++ b/dev/CodeSystem-PSOC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T04:01:15+00:00</t>
+    <t>2026-04-13T08:21:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
